--- a/filer/21093939_rice.xlsx
+++ b/filer/21093939_rice.xlsx
@@ -639,7 +639,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse B · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/21093939_rice.xlsx
+++ b/filer/21093939_rice.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -653,7 +653,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -668,35 +668,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1522,35 +1522,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2856,35 +2856,35 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
@@ -3998,19 +3998,19 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
@@ -4116,19 +4116,19 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
@@ -4426,6 +4426,13 @@
       <c r="F91" s="13">
         <f>IFERROR($F$33/($F$58+0)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4457,19 +4464,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4527,19 +4534,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>22375</v>
+        <v>27798</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>27798</v>
+        <v>25026</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>25026</v>
+        <v>29460</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>29460</v>
+        <v>26154</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>26154</v>
+        <v>31724</v>
       </c>
     </row>
     <row r="7">
@@ -4549,19 +4556,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>17593</v>
+        <v>18923</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>18923</v>
+        <v>20654</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>20654</v>
+        <v>22066</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>22066</v>
+        <v>21384</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>21384</v>
+        <v>23641</v>
       </c>
     </row>
     <row r="8">
@@ -4578,19 +4585,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>1120</v>
+        <v>239</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>239</v>
+        <v>1377</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>1377</v>
+        <v>2584</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>2584</v>
+        <v>2142</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>2142</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -4599,17 +4606,15 @@
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -4618,19 +4623,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>3661</v>
+        <v>8635</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>8635</v>
+        <v>2995</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>2995</v>
+        <v>4798</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>4798</v>
+        <v>2628</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>2628</v>
+        <v>7754</v>
       </c>
     </row>
     <row r="12">
@@ -4652,19 +4657,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>164</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -4674,19 +4679,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>408</v>
+        <v>582</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>582</v>
+        <v>934</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>934</v>
+        <v>89</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>89</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15">
@@ -4708,19 +4713,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>3310</v>
+        <v>8287</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>8287</v>
+        <v>2543</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2543</v>
+        <v>3993</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>3993</v>
+        <v>2703</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>2703</v>
+        <v>7706</v>
       </c>
     </row>
     <row r="17">
@@ -4730,19 +4735,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>749</v>
+        <v>1850</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>1850</v>
+        <v>608</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>608</v>
+        <v>932</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>932</v>
+        <v>633</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>633</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="18">
@@ -4752,19 +4757,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>2562</v>
+        <v>6437</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>6437</v>
+        <v>1935</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1935</v>
+        <v>3061</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>3061</v>
+        <v>2070</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>2070</v>
+        <v>5964</v>
       </c>
     </row>
     <row r="19">
@@ -4774,19 +4779,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="C19" s="16" t="n">
         <v>43</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>37</v>
-      </c>
       <c r="D19" s="16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -4830,19 +4835,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4851,16 +4856,16 @@
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n">
+        <v>2072</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>127</v>
+      </c>
+      <c r="F2" s="16" t="n">
         <v>0</v>
-      </c>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n">
-        <v>2072</v>
-      </c>
-      <c r="F2" s="16" t="n">
-        <v>127</v>
       </c>
     </row>
     <row r="3">
@@ -4894,19 +4899,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>193</v>
+        <v>2574</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>2574</v>
+        <v>4440</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>4440</v>
+        <v>179</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>267</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6">
@@ -4916,19 +4921,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>273</v>
+        <v>134</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>134</v>
+        <v>607</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>607</v>
+        <v>681</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>681</v>
+        <v>579</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>579</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7">
@@ -4950,19 +4955,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>466</v>
+        <v>2708</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>2708</v>
+        <v>5047</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>5047</v>
+        <v>861</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>846</v>
+        <v>729</v>
       </c>
     </row>
     <row r="9">
@@ -4984,19 +4989,19 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>1644</v>
+        <v>1633</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1638</v>
+        <v>1647</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>1647</v>
+        <v>1457</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>1457</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="11">
@@ -5006,19 +5011,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>1644</v>
+        <v>1633</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>1638</v>
+        <v>1647</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>1647</v>
+        <v>1457</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>1457</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="12">
@@ -5028,19 +5033,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>2111</v>
+        <v>4341</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>4341</v>
+        <v>6684</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>6684</v>
+        <v>4579</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>4579</v>
+        <v>2430</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>2430</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="13">
@@ -5061,9 +5066,7 @@
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="16" t="n"/>
       <c r="E14" s="16" t="n"/>
@@ -5076,19 +5079,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>9506</v>
+        <v>16774</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>16774</v>
+        <v>21502</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>21502</v>
+        <v>18221</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>18221</v>
+        <v>17649</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>17649</v>
+        <v>18575</v>
       </c>
     </row>
     <row r="16">
@@ -5098,19 +5101,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>12272</v>
+        <v>20647</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>20647</v>
+        <v>24883</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>24883</v>
+        <v>22772</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>22772</v>
+        <v>26206</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>26206</v>
+        <v>26030</v>
       </c>
     </row>
     <row r="17">
@@ -5120,19 +5123,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>8073</v>
+        <v>9266</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>9266</v>
+        <v>7279</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>7279</v>
+        <v>7837</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>7837</v>
+        <v>8538</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>8538</v>
+        <v>9533</v>
       </c>
     </row>
     <row r="18">
@@ -5142,19 +5145,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>1802</v>
+        <v>2089</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>2089</v>
+        <v>847</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>847</v>
+        <v>2695</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>2695</v>
+        <v>811</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="19">
@@ -5164,19 +5167,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>1590</v>
+        <v>2653</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>2653</v>
+        <v>642</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>642</v>
+        <v>331</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>331</v>
+        <v>1009</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>1009</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="20">
@@ -5186,19 +5189,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>475</v>
+        <v>965</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>965</v>
+        <v>755</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>755</v>
+        <v>1055</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>1055</v>
+        <v>983</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>983</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="21">
@@ -5208,15 +5211,15 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>381</v>
-      </c>
-      <c r="C21" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="C21" s="16" t="n"/>
       <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
+      <c r="E21" s="16" t="n">
+        <v>71</v>
+      </c>
       <c r="F21" s="16" t="n">
-        <v>71</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22">
@@ -5250,19 +5253,19 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>12321</v>
+        <v>14973</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>14973</v>
+        <v>9524</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>9524</v>
+        <v>11918</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>11918</v>
+        <v>11411</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>11411</v>
+        <v>13456</v>
       </c>
     </row>
     <row r="25">
@@ -5284,19 +5287,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>6706</v>
+        <v>178</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>178</v>
+        <v>1275</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>1275</v>
+        <v>682</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>682</v>
+        <v>365</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>365</v>
+        <v>957</v>
       </c>
     </row>
     <row r="27">
@@ -5306,19 +5309,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>31299</v>
+        <v>35798</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>35798</v>
+        <v>35682</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>35682</v>
+        <v>35372</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>35372</v>
+        <v>37981</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>37981</v>
+        <v>40443</v>
       </c>
     </row>
     <row r="28">
@@ -5328,19 +5331,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>33410</v>
+        <v>40139</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>40139</v>
+        <v>42366</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>42366</v>
+        <v>39951</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>39951</v>
+        <v>40411</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>40411</v>
+        <v>43079</v>
       </c>
     </row>
     <row r="29">
@@ -5420,19 +5423,19 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>21378</v>
+        <v>22815</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>22815</v>
+        <v>23250</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>23250</v>
+        <v>23911</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>23911</v>
+        <v>24181</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>24181</v>
+        <v>27545</v>
       </c>
     </row>
     <row r="35">
@@ -5442,19 +5445,19 @@
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>25490</v>
+        <v>28927</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>28927</v>
+        <v>25862</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>25862</v>
+        <v>27423</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>27423</v>
+        <v>27093</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>27093</v>
+        <v>31257</v>
       </c>
     </row>
     <row r="36">
@@ -5463,19 +5466,19 @@
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
+      <c r="B36" s="16" t="n">
+        <v>295</v>
+      </c>
       <c r="C36" s="16" t="n">
-        <v>295</v>
+        <v>715</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>715</v>
+        <v>290</v>
       </c>
       <c r="E36" s="16" t="n">
-        <v>290</v>
-      </c>
-      <c r="F36" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -5483,19 +5486,19 @@
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
+      <c r="B37" s="16" t="n">
+        <v>295</v>
+      </c>
       <c r="C37" s="16" t="n">
-        <v>295</v>
+        <v>715</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>715</v>
+        <v>290</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>290</v>
-      </c>
-      <c r="F37" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
@@ -5528,19 +5531,19 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
+        <v>1326</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>8619</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>3518</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>4074</v>
+      </c>
+      <c r="F40" s="16" t="n">
         <v>0</v>
-      </c>
-      <c r="C40" s="16" t="n">
-        <v>1326</v>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>8619</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>3518</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>4074</v>
       </c>
     </row>
     <row r="41">
@@ -5562,19 +5565,19 @@
         </is>
       </c>
       <c r="B42" s="16" t="n">
-        <v>3169</v>
+        <v>6021</v>
       </c>
       <c r="C42" s="16" t="n">
-        <v>6021</v>
+        <v>5327</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>5327</v>
+        <v>4073</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>4073</v>
+        <v>5747</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>5747</v>
+        <v>5083</v>
       </c>
     </row>
     <row r="43">
@@ -5584,14 +5587,16 @@
         </is>
       </c>
       <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
+      <c r="C43" s="16" t="n">
+        <v>39</v>
+      </c>
       <c r="D43" s="16" t="n">
-        <v>39</v>
-      </c>
-      <c r="E43" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
@@ -5600,19 +5605,19 @@
         </is>
       </c>
       <c r="B44" s="16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C44" s="16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>1</v>
+        <v>482</v>
       </c>
     </row>
     <row r="45">
@@ -5621,9 +5626,7 @@
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>1026</v>
-      </c>
+      <c r="B45" s="16" t="n"/>
       <c r="C45" s="16" t="n"/>
       <c r="D45" s="16" t="n"/>
       <c r="E45" s="16" t="n"/>
@@ -5635,18 +5638,20 @@
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
+      <c r="B46" s="16" t="n">
+        <v>1175</v>
+      </c>
       <c r="C46" s="16" t="n">
-        <v>1175</v>
+        <v>187</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>187</v>
+        <v>1357</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>1357</v>
+        <v>994</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>994</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="47">
@@ -5656,19 +5661,19 @@
         </is>
       </c>
       <c r="B47" s="16" t="n">
-        <v>3718</v>
+        <v>2390</v>
       </c>
       <c r="C47" s="16" t="n">
-        <v>2390</v>
+        <v>1618</v>
       </c>
       <c r="D47" s="16" t="n">
-        <v>1618</v>
+        <v>3287</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>3287</v>
+        <v>2306</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>2306</v>
+        <v>4089</v>
       </c>
     </row>
     <row r="48">
@@ -5680,9 +5685,11 @@
       <c r="B48" s="16" t="n"/>
       <c r="C48" s="16" t="n"/>
       <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
+      <c r="E48" s="16" t="n">
+        <v>104</v>
+      </c>
       <c r="F48" s="16" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49">
@@ -5692,19 +5699,19 @@
         </is>
       </c>
       <c r="B49" s="16" t="n">
-        <v>7920</v>
+        <v>10917</v>
       </c>
       <c r="C49" s="16" t="n">
-        <v>10917</v>
+        <v>15790</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>15790</v>
+        <v>12238</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>12238</v>
+        <v>13318</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>13318</v>
+        <v>11822</v>
       </c>
     </row>
     <row r="50">
@@ -5714,19 +5721,19 @@
         </is>
       </c>
       <c r="B50" s="16" t="n">
-        <v>7920</v>
+        <v>10917</v>
       </c>
       <c r="C50" s="16" t="n">
-        <v>10917</v>
+        <v>15790</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>15790</v>
+        <v>12238</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>12238</v>
+        <v>13318</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>13318</v>
+        <v>11822</v>
       </c>
     </row>
     <row r="51">
@@ -5736,19 +5743,19 @@
         </is>
       </c>
       <c r="B51" s="16" t="n">
-        <v>33410</v>
+        <v>40139</v>
       </c>
       <c r="C51" s="16" t="n">
-        <v>40139</v>
+        <v>42366</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>42366</v>
+        <v>39951</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>39951</v>
+        <v>40411</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>40411</v>
+        <v>43079</v>
       </c>
     </row>
   </sheetData>
@@ -5787,13 +5794,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6507,7 +6514,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6625,7 +6632,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6801,7 +6808,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7024,27 +7031,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7072,9 +7079,11 @@
       <c r="D3" s="35" t="n"/>
       <c r="E3" s="35" t="n"/>
       <c r="F3" s="35" t="n"/>
-      <c r="G3" s="35" t="n"/>
+      <c r="G3" s="35" t="n">
+        <v>94</v>
+      </c>
       <c r="H3" s="35" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I3" s="36" t="inlineStr">
         <is>
